--- a/Excel/4_7_ManureManagement_OtherLivestock_WIP_v01.prename.bak.xlsx
+++ b/Excel/4_7_ManureManagement_OtherLivestock_WIP_v01.prename.bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE17963B-FA6F-489F-AF0C-5A1ADAC47B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC90442-0B3A-4D2C-9068-B004843A827A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="1410" windowWidth="36255" windowHeight="19140" firstSheet="3" activeTab="8" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" firstSheet="8" activeTab="11" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -24,9 +24,12 @@
     <sheet name="4.7.1.7-8 Soil Leaching Runoff" sheetId="104" r:id="rId9"/>
     <sheet name="Constants - Other Livestock" sheetId="79" r:id="rId10"/>
     <sheet name="Constants - Livestock" sheetId="43" r:id="rId11"/>
-    <sheet name="Constants - Common" sheetId="105" r:id="rId12"/>
+    <sheet name="Constants - Common" sheetId="106" r:id="rId12"/>
     <sheet name="Acknowledgements" sheetId="72" r:id="rId13"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId14"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -183,6 +186,7 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonCropping_InputFunctions.CommonCropping_CalculateFractionResidueRemoved">_xlfn.LAMBDA(_xlpm.TotalResidue,_xlpm.AmountRemoved, (_xlpm.AmountRemoved * 10 ^ 3) / (_xlpm.TotalResidue * 10 ^ 3))</definedName>
     <definedName name="CommonCropping_InputFunctions.CommonCropping_CalculateHarvestIndex">_xlfn.LAMBDA(_xlpm.CropType,_xlpm.CropTypeArray,_xlpm.ResidueCropRatioArray, 1 / (1 + Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.CropType, _xlpm.CropTypeArray, _xlpm.ResidueCropRatioArray)))</definedName>
     <definedName name="CommonCropping_InputFunctions.CommonCropping_CalculateResidueCropRatio">_xlfn.LAMBDA(_xlpm.HarvestIndex, (1 - _xlpm.HarvestIndex) / _xlpm.HarvestIndex)</definedName>
@@ -500,7 +504,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="246">
   <si>
     <t>Home</t>
   </si>
@@ -1515,9 +1519,6 @@
   </si>
   <si>
     <t>EFNi &amp; EFN2Oi</t>
-  </si>
-  <si>
-    <t>N2O</t>
   </si>
 </sst>
 </file>
@@ -9274,6 +9275,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -9379,20 +9400,20 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{FC6B6FDB-39C9-44DB-B07A-596281048476}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A41FE641-FD24-4011-B6D1-271253F24CFF}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8D9D8EA2-A68D-4614-85BA-0F315B28B22B}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{A8F3C1AC-508B-4536-8239-134C3D148801}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7CA81194-EB21-4E83-AA73-457DF5248415}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{3EFD1E1D-D4DE-40E7-9831-479A587E5AB6}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4F4710F9-2D92-4A41-8629-4F34BD7C3469}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{395EFB98-1733-420D-99BF-6EC3EBCC9856}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9401,12 +9422,12 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{46EB4109-7A16-4322-92E0-36A58C39492C}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3E885029-CC59-48FA-B552-3934B9F87589}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{E8BE105B-ADA6-463C-8A5C-64F46434D3D0}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{65328C0F-FEAD-4BA9-982A-22B3DA1C8B3D}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9415,16 +9436,16 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{CB3368B1-94D6-4BF8-8F7A-54D84C083EBC}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{D70570E6-5E1B-40F6-975E-69706A378F03}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AF27F796-517A-4A4F-883A-20B6B44039D7}" name="Gas">
+    <tableColumn id="1" xr3:uid="{5D42CBEF-9207-49EB-B3A6-867F5E16654B}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{22C2AF2C-B7BB-4FFE-9EA6-36E8CE178CE5}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{31D9DC9C-FD19-4007-B86F-237AA3FC236F}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9433,7 +9454,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{445C0DFE-1BFA-4B65-999E-791F1349C6F5}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{9C797D4E-0F11-48F8-92E3-531E551A179F}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9442,19 +9463,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BDD6D4C0-9572-497D-BA81-056A4E2F1000}" name="Gas">
+    <tableColumn id="1" xr3:uid="{57B56706-E8DD-4393-8C9E-48CA3456EB91}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9802BAEC-70C6-4B67-95CC-E43570FEBB9A}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{A547F130-C66F-4B63-A2BD-84DA22458231}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{728278C4-1ECA-47B1-83C5-9070B3154751}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{9BBF1D7B-03F9-4861-A935-EB760E38D571}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F1AF8D8D-558C-478C-88C0-D7FFECE801AE}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{E86E9F79-3E7B-4D96-8772-BED366CCD8D6}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F5B19595-DA9C-4C87-A41E-0CF7A73B4D7F}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{45E14761-F207-44E2-80E9-7496D68347D8}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9463,7 +9484,7 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{39B2BF63-4ECF-4EC3-8CF2-9D62F8799ED7}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{BF8716FB-75BA-4CFA-98D2-E5A394AA4FD1}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9483,52 +9504,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{C2DCCDDC-F0D6-46F3-9F31-1FB81485F9B7}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{1F756ECE-8D0E-46EB-AA15-851322033D31}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{085D949F-3C9F-4972-865D-9738FC7D39E4}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{E4E36567-BBA2-4402-A05A-770FAF31C38A}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8E99D282-BC43-4434-8796-AEDEF3920BE4}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{D6E8900F-E2A4-4F43-862C-139252D3337C}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8A9F1878-474B-4CA1-9D44-B0FB65DEB401}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{4BAD5116-B162-449C-8438-48EE46F623C9}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{04EE6251-A51B-478A-BC75-F69CF15D0497}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{E3DBB9F9-9030-4FF2-93F7-1046C63305FF}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{163A4D02-6241-4478-BC63-B8332314253F}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{D19E1AF7-C103-4465-827A-272966E9BB2B}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{0B7B69B5-7FC2-4DC1-B266-23B289F65875}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{5C718C43-26C6-43E1-B01C-9B8888AF5CD7}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{543AE399-BD8B-43A0-ADE9-FCAB4605503B}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{3F0FA349-758F-440D-8B9F-92BEDB006B3B}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{209AB0DF-461D-4417-A84F-A746C445D0DF}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{6FE4C191-1D7C-447A-807F-52BAA1F83C1B}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{30AC38E7-F0DC-44EE-8147-A9FAA73374BE}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{C465259B-535A-4418-9C56-99040421033F}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{6A50662F-EECF-4250-A6E7-B71C10F7F5B0}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{049DB580-CA31-478D-A316-B9826DC5976C}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{BB06D093-E69A-4676-BD96-D9CBAF229E1B}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{E28D5CDC-6CDE-40AC-BB69-B520E6BE9ECE}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{A54A01F4-29B9-4008-8B43-595A9603406D}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{28DEE6A7-2DC0-4DF3-BA96-82E0B5206A88}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{808C5875-68DD-448E-8572-98E488BDEC32}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{3CEAC3FE-E190-4B17-A0E5-E93072D2EE0C}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{14D0D466-C603-44F1-9239-488927F5D894}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{B2607A8A-4828-4A7F-8B59-AFDF70121EA9}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{D4DF1A32-A877-425B-887C-8CBD6B3A674F}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{EE9AE32D-CD32-49F5-8434-FED04B1C7173}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9537,16 +9558,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{F85B6BA6-EBDD-4917-8629-AA549398D3D8}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{CE480793-0C84-4828-8E5A-1C1FEE1D5CCF}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F9E03CCA-29B0-4DFA-BB92-47A4DA346452}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{FC589081-50C7-4011-B899-F7D6142FB1B3}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4F3558C5-FC0E-4FAD-B715-8FF569D9AB01}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{B9257959-AB83-4C24-830F-528097C2CA9C}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9555,7 +9576,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{3000B7EA-5CFD-4C95-96DA-A6934D74B474}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{3EE2AED7-0B26-4BC6-88AE-00251A82554D}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9563,16 +9584,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8F276D39-DE04-4A20-942C-5A83D3A7502B}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{3DE50BA4-F469-4427-8A0D-5A3CEB07043F}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D4915A01-DA87-4C09-B32E-662E37E3A0B4}" name="MAT">
+    <tableColumn id="2" xr3:uid="{8E68245D-BCA1-4649-B2EE-C522A8374FA9}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6EC2186D-66AB-4B7E-A085-EE28E052E5B0}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{B64B737B-2A04-483B-B501-A86581036C65}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{DCE40066-03DA-4742-8D0B-AA1C523EB845}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{646A3698-41BB-45F3-83DA-ACD16CB207F6}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9581,7 +9602,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{398397E7-170E-47D5-84AC-DBDA25FEEB3B}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{BC8D0DD2-CE02-4850-8FA0-D007CF049344}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9589,16 +9610,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6175785E-683F-4FC6-A3DF-4F1B35AC8EE2}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{54ACFB07-6FFC-40E9-A276-405583193462}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3FDE8615-A5D5-46C7-801B-A64A34EF39B7}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{ADFC501F-3203-4414-AAA8-28B1FA2E0C2B}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{77894486-2DB0-4DB6-8743-6B8F0C94E39F}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{124A4494-0696-49EF-9847-DF0516EDC25B}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{940F6A47-B6FE-4F96-80ED-598E434A30F1}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{B6679ACD-E8EC-4022-AABD-258C8AE332FD}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9607,16 +9628,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{A03D6921-AF80-420C-80B9-07981D56513F}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{23A63569-D178-4419-BAF4-DAB563E8787D}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1A3D1EFC-C92D-4747-813D-931E4925A028}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{75E2EC06-3B7D-4F01-9A59-DAB1590DE1F5}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A577D465-C3A8-4623-9CED-76461D6E142E}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{27708231-DEF1-40F7-8D3F-36E0953E0D0A}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9643,16 +9664,16 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{48E39D59-C131-4396-8A2A-D8C57E50B4BC}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{D9DB5EE2-A508-4A8B-9D8A-E5174651F0F9}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{653FBE11-AAB4-4E3C-892D-D288E9F2B7B6}" name="Data source">
+    <tableColumn id="1" xr3:uid="{87DEC54C-9713-4A0D-A35D-35AF849EA4BB}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AA539FCD-8160-447C-95D7-993FF3D9EE37}" name="Data score">
+    <tableColumn id="2" xr3:uid="{B286ACBB-85D4-42E3-9839-DEBBE850C27D}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9661,16 +9682,16 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{4C35AF62-1A17-42DB-871F-D7B2AFBD643D}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{C34D716F-1DB3-439C-8DB0-DC72715090EB}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{98A0A3BA-3AA7-49C3-89F0-7DECBD7F87E0}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{42786E11-D892-4920-9A89-7DF8F5B57ECD}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{83D3C20F-03AF-42A2-AFAF-E188DFDAAB7C}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{F8ACB435-9333-46C3-9CE1-E917C7F45FDD}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9679,7 +9700,7 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{D09402D6-A961-44A3-AB2F-80A4A04C56EF}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{42A5A179-062A-4094-9354-171B66E400CA}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9688,19 +9709,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E8BD89A5-3583-4A16-91E6-F8D32C1D9C18}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{F5B173F1-A248-4BD9-B9FC-86FA001CA6AE}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{98AB8D20-DC97-47F4-B0EB-3D2D9CF6A6B4}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{C0ED70CC-0391-4E93-8763-68B04285CCDA}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F3048E47-EFF4-498E-8D46-E4F8D0BE9AE1}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{B09AB8AB-845B-41E7-9A54-BA87DBCAD370}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{61DCF957-F499-4D35-A8D1-1B2B14583ADB}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{C5F8F664-9594-4D40-8521-3EFC9630D6D3}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{14739323-C540-4BCB-9A3E-02AD7825C20C}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{605547DF-3047-4079-AB74-0968F15FE282}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9709,16 +9730,16 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{349D3DF0-4C1C-404D-AFC9-22BF53B86C77}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{E3AEA724-B952-497E-A84F-3B5ECBE7B5CF}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3F869A0F-445B-459C-AD76-C43D66243802}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{1CA22ABA-FF81-4B2A-8F64-49727B4BF401}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DA1A4153-2AFC-4A3F-81BD-926EBF6CDAFF}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{06CFAD91-F13C-4026-9DDC-82944352DBB0}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9727,16 +9748,16 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{3DEE1F2F-0CC9-4142-8B7E-092D2682C857}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{49B038DC-D60B-4144-B7FE-A34C8C597FC7}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25AB7809-B0B0-4B3F-B26D-935CF994DD92}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{ADFFE3A2-3C8A-4121-B340-0E2214EC5BA1}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5EB5D3A5-2CB1-4374-AFF4-6292EAB435E6}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2C8D4993-4AE2-4BA6-861D-7C75168C934E}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9745,16 +9766,16 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{E7C16B54-9272-47FD-9DD8-3DD27D1CBD63}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{2268719A-B09A-4A18-B85B-5C47B0058C67}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9E066805-A7A8-42A1-AEAD-2D0A0F98638D}" name="Month">
+    <tableColumn id="1" xr3:uid="{557AFE4A-E50B-48C4-A78F-EDB3E2F5513D}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5FACF69C-E542-4A97-B154-ED182A7D4A65}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2B6FAA2C-6699-4E65-8AF4-7FFB022E013A}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9763,7 +9784,7 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{CA7DDC87-6036-4E12-8133-3018BF6612E1}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{5262288B-DC8C-4220-A8EA-4666AC4AB5ED}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9783,52 +9804,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{D60D1CFA-4A63-42F1-ACE1-82BAE1308656}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{5BE488E9-C88F-4D40-BFE4-2F14BFE204FE}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3C564E27-E185-496B-A330-E4D9605703FD}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{7471337B-A383-48F1-9140-7A247CE94C8C}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A818A779-AFB9-4CE3-8852-0DB2C96ABD11}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9751CF7A-2A90-41C3-B0C7-75B6BE4418D9}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F77A5000-E707-4583-9D8F-45A2A7A1CE49}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{CA5FACFF-2A01-4823-AE11-C25A5DB63212}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{52CDECDF-F499-4FA4-9C30-6699803FC36C}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{AD3B111E-1B73-4EAA-ACFB-B1EA17DB2261}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{395B210D-71D4-4709-ACE9-5F7B69D48D20}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{47E6E961-631F-4462-83C1-CBA267F81DBF}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{CBD9C4B7-DBD3-447B-9516-B01AF2D1EA5E}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{5E5FC724-F551-44A5-B89F-454716A00746}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{4A687C6D-AA56-4AE6-9026-7D85E0E2428C}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{94DCCEDE-8F03-4DCB-BD73-4137AA6BFB7B}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{27A1A806-2F80-4500-B309-D9F79F8565FB}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{D2CE3558-5412-4654-9F72-DA1821CDE596}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{88260F93-4DC8-441A-8187-14BF00D048B8}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{607A79A9-61FE-48BF-BE48-0965C1DF8C73}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{C8E25584-0560-4214-9506-F247C8941C71}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{98F5211C-781C-45BD-AF95-05B148C528F9}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{B1BC0AC2-0009-4CCF-8250-71AE91D3D491}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{154A1334-E483-46FC-9EFD-C7408471DC4C}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{A04E251C-D36B-406C-A4DE-80A4ABE938A3}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{CB4AF493-91F1-476F-AA2D-085C994C3162}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{75EFD31E-5E04-4093-8672-13DAE0D3B3F2}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{6D0E7416-BFEB-44E9-8544-61035BEA7B24}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{4C84D9ED-C72E-4170-B03D-03CAB55BA59F}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{7CBEB24B-DEDB-4F2B-B7E6-E6997FA2618D}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{BDD47183-C151-40B2-85CD-C839C803B2DC}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{4F278C8D-7F75-44BF-809F-EC6F8B2D6E58}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9837,16 +9858,16 @@
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{0BC7828E-6F8E-4059-8196-2C8B1594590D}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="44" xr:uid="{62AA56D9-3B2F-4E1B-88E7-49C1487718EB}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FF8BFB87-4EC2-4DCA-99C7-CC22317FD350}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{1512BED0-98D7-41FD-B812-44719FDE3EC4}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E1F7C91A-9352-4C6F-9C33-48F3841846CA}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{73340C7C-6E56-43EB-8AAB-D3E271491791}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12546,7 +12567,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58CA0CCA-2EBC-4649-BB27-D0768E2C4161}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94F22857-35FF-4100-9097-32B1F6E6B9BB}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12892,9 +12913,6 @@
       <c r="E37" s="39" cm="1">
         <f t="array" ref="E37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>1</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -29174,6 +29192,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -29184,20 +29211,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAxAC8AKAAxACsAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACwAXABuACAAIAAgACAAKAAxAC0ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAKQAvAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACwAIABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACwAXABuACAAIAAgACAAKABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACoAMQAwAF4AMwApAC8AKABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAqADEAMABeADMAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgAxADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABFAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AeQBlAGEAcgApACAAKABNAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQAIAAvACAAaABlAGEAZAAgAC8AIAB5AGUAYQByAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4AMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAXAAiACwAIABcACIATQBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAANgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAbwBhAHQAcwBcACIALAAgADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADQANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAcABhAGMAYQBzAFwAIgAsACAAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgAyADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHAAcgBvAGQAdQBjAGUAZAAgAGIAeQAgAGUAYQBjAGgAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAFYAUwAvAGgAZQBhAGQALwBkAGEAeQApACAAKABWAFMAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHAAcgBvAGQAdQBjAGUAZAAgAGIAeQAgAGUAYQBjAGgAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABWAFMAIAAvACAAaABlAGEAZAAgAC8AIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4AMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAFYAUwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMgAuADcAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHIAXAAiACwAIAAwAC4AOQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAAMgAuADcAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAcABhAGMAYQBzAFwAIgAsACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADIALgA3ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMAAuADkAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAAwAC4AMwA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADMAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAHAAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAKABrAGcAIABOADIATwAvAGgAZQBhAGQALwB5AGUAYQByACkAIAAoAE4ARQBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAHAAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBFAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAvACAAaABlAGEAZAAgAC8AIAB5AGUAYQByAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAXAAiACwAIABcACIATgBFAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAAzADkALgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAbwBhAHQAcwBcACIALAAgADcALgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHIAXAAiACwAIAAxADMALgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAAMwA5AC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAcABhAGMAYQBzAFwAIgAsACAANwAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAzADkALgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADEAMwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAANwAuADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgA0ADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABzACAAKABXAGMAbwApACAAKABrAGcAKQAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFcAYwBvAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQAgAGoAXAAiACwAIABcACIAQQB2AGUAcgBhAGcAZQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAXAAiACwAIABcACIAQQB2AGUAcgBhAGcAZQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAAzADMANgAsACAAXAAiAC0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAbwBhAHQAcwBcACIALAAgADMAMwAsACAAXAAiADIAOABrAGcAIAAtACAAbABvAHcAIABwAHIAbwBkAHUAYwB0AGkAdgBpAHQAeQAgAHMAeQBzAHQAZQBtAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAbwBhAHQAcwBcACIALAAgADMAMwAsACAAXAAiADUAMABrAGcAIAAtACAAaABpAGcAaAAgAHAAcgBvAGQAdQBjAHQAaQB2AGkAdAB5ACAAcwB5AHMAdABlAG0AcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADEAMgAwACwAIAAxADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADIAMQA3ACwAIAA1ADcAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAcABhAGMAYQBzAFwAIgAsACAAXAAiAC0AXAAiACwAIAA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAzADcANwAsACAANQA1ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMQAzADAALAAgADIANAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADEAMgAwACwAIAAxADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAZgBlAHIAZQBuAGMAZQBcACIALAAgAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFQAYQBiAGwAZQAgADEAMABBAC4ANQAgAFsAMgBdAFwAIgAsACAAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAVABhAGIAbABlACAAMQAwAC4AMQAwACAAWwAyAF0AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgA1ADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAIABpAG4AIABlAGEAYwBoACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAE0AUwBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAIABpAG4AIABlAGEAYwBoACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4ANQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAEEAUwBcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBJAEMAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgA2ADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAcABlAHIAIAByAGUAZwBpAG8AbgAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHIAZQBnAGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAEMARgBpAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4ANgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4AOAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAEEAUwBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADYAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AWAA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAAoAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwApACAAKABCAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAE8AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAbQAzACAAQwBIADQAIAAvACAAawBnACAAVgBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgBYAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABUAGgAZQByAGUAIAB3AGUAcgBlACAAbgBvACAAdgBhAGwAdQBlAHMAIABpAG4AIABWAEUARQBSAEcAIABzAG8AIAB0AGgAaQBzACAAZABhAHQAYQAgAGgAYQBzACAAYgBlAGUAbgAgAGcAZQBuAGUAcgBhAHQAZQBkACAAYgB5ACAAdQBzAGkAbgBnACAAZABvAGMAdQBtAGUAbgB0AGUAZAAgAEIATwAgAHYAYQBsAHUAZQBzACAAZgByAG8AbQAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBCAE8AXAAiACwAIABcACIAVABhAGsAZQBuACAAZgByAG8AbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADAALgAxADkALAAgAFwAIgBGAGUAZQBkAGwAbwB0ACwAIABQAGEAcwB0AHUAcgBlACAAYgBlAGUAZgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMAAuADEAOQAsACAAXAAiAEYAZQBlAGQAbABvAHQALAAgAFAAYQBzAHQAdQByAGUAIABiAGUAZQBmAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAAwAC4AMwA2ACwAIABcACIAUABvAHUAbAB0AHIAeQAgAC0AIABtAGUAYQB0ACAAYwBoAGkAYwBrAGUAbgBzAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADcALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIAMQApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANwA6ACAATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAALQAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANwAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AYQBuAHUAcgBlACAATQBlAHQAaABhAG4AZQAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABvAGYAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawBcAG4ARQBfAEMASAA0AFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AEMASAA0AH0APQBcAFwAcwB1AG0AXwBqAFwAXABzAHUAbQBfAG0AKABOAF8AagBcAFwAdABpAG0AZQBzACAATQBfAGoAbQBcAFwAdABpAG0AZQBzACAAMwA2ADUAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATgBfAGoAIAA9ACAAYQB2AGUAcgBhAGcAZQAgAGEAbgBuAHUAYQBsACAAbgB1AG0AYgBlAHIAIABvAGYAIABsAGkAdgBlAHMAdABvAGMAawAgAHAAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAagAgACgAaABlAGEAZAApAFwAbgBNAF8AagBtACAAPQAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoALAAgAE0AXwBqAG0ALABcAG4AIAAgACAAIABTAFUATQAoAE4AXwBqACAAKgAgAE0AXwBqAG0AIAAqACAAMwA2ADUAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABvAGYAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA3AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAQwBIADQAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAG0AKABOAF8AagBcAFwAdABpAG0AZQBzACAATQBfAGoAbQBcAFwAdABpAG0AZQBzACAAMwA2ADUAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBhAHYAZQByAGEAZwBlACAAYQBuAG4AdQBhAGwAIABuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIABqAFwAIgAsACAAXAAiAGgAZQBhAGQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AagBtAFwAIgAsACAAXAAiAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADcALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQBcACIALAAgAFwAIgBtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAEEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBNAF8AagBtAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAGoAbQA9AFYAUwBfAGoAXABcAHQAaQBtAGUAcwAgAEIAXwBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAG0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AaQBtAFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXABuAFYAUwBfAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAawBnAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEIAXwBPACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAKABtADMAIABDAEgANAAvAGsAZwAgAFYAUwApAFwAbgBNAE0AUwBfAG0AIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlACAAaQBuACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAbgBNAEMARgBfAGkAbQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoAGsAZwAvAG0AMwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFYAUwBfAGoALAAgAEIAXwBPACwAIABNAE0AUwBfAG0ALAAgAE0AQwBGAF8AaQBtACwAIAByAGgAbwAsAFwAbgAgACAAIAAgAFYAUwBfAGoAIAAqACAAQgBfAE8AIAAqACAATQBNAFMAXwBtACAAKgAgAE0AQwBGAF8AaQBtACAAKgAgAHIAaABvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAbQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADcALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQB9AD0AVgBTAF8AagBcAFwAdABpAG0AZQBzACAAQgBfAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AbQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAIABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAF8ATwBcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIALAAgAFwAIgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAIABpAG4AIABlAGEAYwBoACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAXwBpAG0AXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABlACAAYQBuAGQAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALAAgAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBrAGcALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALAAgAFwAIgB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAXwBPAFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBfAGkAbQBcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALAAgAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBrAGcALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIALAAgAFwAIgBkAGUAZwByAGUAZQBzACAAQwBlAGwAcwBpAHUAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA3ADoAIABNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAAtACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA3AC4AMQAuADMAIABNAGUAdABoAG8AZAAgADEAIAAtACAAUwBvAGkAbAAgAEQAaQByAGUAYwB0ACAATgAyAE8AIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXABuAEQAaQByAGUAYwB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcwBvAGkAbABzACAAZgByAG8AbQAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABvAGYAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIAB0AG8AIABwAGEAcwB0AHUAcgBlAFwAbgBFAF8ATgAyAE8AZABpAHIAXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AQQBFAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFAAUgBQAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEEARQAgAD0AIABhAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAE4ALwB5AGUAYQByACkAXABuAEUARgBfAFAAUgBQACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAdABvACAAcwBvAGkAbAAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGQAZQBwAG8AcwBpAHQAZQBkACkAXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBFACwAIABFAEYAXwBQAFIAUAAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAQQBFACAAKgAgAEUARgBfAFAAUgBQACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIABzAG8AaQBsAHMAIABmAHIAbwBtACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAHQAbwAgAHAAYQBzAHQAdQByAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBkAGkAcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPACwAZABpAHIAfQA9AEEARQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBQAFIAUAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARQBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACwAIABcACIAawBnACAATgAvAHkAZQBhAHIAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANwAuADEALgAzACwAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUABSAFAAXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABkAGUAcABvAHMAaQB0AGUAZABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALAAgAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgB3AGUAdAAgAG8AcgAgAGQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADIAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFQAbwBQAGEAcwB0AHUAcgBlAFwAbgBBAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdABvACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAbgBBAEUAXABuAGsAZwAgAE4ALwB5AGUAYQByAFwAbgBBAEUAPQBcAFwAcwB1AG0AXwBqACgATgBfAGoAXABcAHQAaQBtAGUAcwAgAE4ARQBfAGoAXABcAHQAaQBtAGUAcwAgADMANgA1ACkAXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAbABpAHYAZQBzAHQAbwBjAGsAIABvAGYAIABlAGEAYwBoACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAagAgACgAaABlAGEAZAApAFwAbgBOAEUAXwBqACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIABqACAAKABrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoALAAgAE4ARQBfAGoALABcAG4AIAAgACAAIABOAF8AagAgACoAIABOAEUAXwBqACAAKgAgADMANgA1AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AG8AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADIAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFQAbwBQAGEAcwB0AHUAcgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADIAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFQAbwBQAGEAcwB0AHUAcgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAvAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADIAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFQAbwBQAGEAcwB0AHUAcgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA3AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAKABOAF8AagBcAFwAdABpAG0AZQBzACAATgBFAF8AagBcAFwAdABpAG0AZQBzACAAMwA2ADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGoAXAAiACwAIABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABsAGkAdgBlAHMAdABvAGMAawAgAG8AZgAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIABqAFwAIgAsACAAXAAiAGgAZQBhAGQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEUAXwBqAFwAIgAsACAAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIABqAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsACAAXAAiAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA3ADoAIABNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAAtACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA3AC4AMQAuADUAIABNAGUAdABoAG8AZAAgADEAIAAtACAAUwBvAGkAbAAgAEEAdABtAG8AcwBwAGgAZQByAGkAYwAgAEQAZQBwAG8AcwBpAHQAaQBvAG4AIABOADIATwAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBcAG4AQQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcAG4ARQBfAE4AMgBPAGEAZABcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwAsAGEAZAB9AD0ATQBfAHsAdgBvAGwAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBNAF8AdgBvAGwAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACAAKABrAGcAIABOACkAXABuAEUARgBfAE4AMgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAHYAbwBsACwAIABFAEYAXwBOADIATwAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAATQBfAHYAbwBsACAAKgAgAEUARgBfAE4AMgBPACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAGEAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADEALgA1ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPACwAYQBkAH0APQBNAF8AewB2AG8AbAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAHYAbwBsAFwAIgAsACAAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADcALgAxAC4ANQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAIABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAFwAIgAsACAAXAAiAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAbgBNAF8AdgBvAGwAXABuAGsAZwAgAE4AXABuAE0AXwB7AHYAbwBsAH0APQBBAEUAXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAbgBBAEUAIAA9ACAAYQBuAG4AdQBhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABiAHkAIABlAGEAYwBoACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAKABrAGcAIABOAC8AeQBlAGEAcgApAFwAbgBGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAgACgAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBQAGEAcwB0AHUAcgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEARQAsACAARgByAGEAYwBHAEEAUwBNAHMAbwBpAGwALABcAG4AIAAgACAAIABBAEUAIAAqACAARgByAGEAYwBHAEEAUwBNAHMAbwBpAGwAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AdgBvAGwAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADEALgA1ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewB2AG8AbAB9AD0AQQBFAFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARQBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACwAIABcACIAawBnACAATgAvAHkAZQBhAHIAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGIAeQAgADQALgA3AC4AMQAuADMALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADcAOgAgAE0AYQBuAHUAcgBlACAATQBhAG4AYQBnAGUAbQBlAG4AdAAgAC0AIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADcALgAxAC4ANwAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABTAG8AaQBsACAATABlAGEAYwBoAGkAbgBnACAAQQBuAGQAIABSAHUAbgBvAGYAZgAgAE4AMgBPACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBcAG4ATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcAG4ARQBfAE4AMgBPAGwAZQBhAGMAaABcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwAsAGwAZQBhAGMAaAB9AD0ATQBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAE0AXwBsAGUAYQBjAGgAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKABrAGcAIABOACkAXABuAEUARgBfAGwAZQBhAGMAaAAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAbgBDAF8ATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbABlAGEAYwBoACwAIABFAEYAXwBsAGUAYQBjAGgALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0AXwBsAGUAYQBjAGgAIAAqACAARQBGAF8AbABlAGEAYwBoACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AbABlAGEAYwBoAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADcALgAxAC4ANwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPACwAbABlAGEAYwBoAH0APQBNAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGwAZQBhAGMAaABcACIALAAgAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA3AC4AMQAuADcALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBsAGUAYQBjAGgAXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALAAgAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgBNAF8AbABlAGEAYwBoAFwAbgBrAGcAIABOAFwAbgBNAF8AewBsAGUAYQBjAGgAfQA9AEEARQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBXAGUAdABcAFwAdABpAG0AZQBzACAARgByAGEAYwBMAEUAQQBDAEgAXABuAEEARQAgAD0AIABhAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAE4ALwB5AGUAYQByACkAXABuAEYAcgBhAGMAVwBlAHQAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAEYAcgBhAGMATABFAEEAQwBIACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAbgBpAHQAcgBvAGcAZQBuACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAEUALAAgAEYAcgBhAGMAVwBlAHQALAAgAEYAcgBhAGMATABFAEEAQwBIACwAXABuACAAIAAgACAAQQBFACAAKgAgAEYAcgBhAGMAVwBlAHQAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGwAZQBhAGMAaABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADEALgA3ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAbABlAGEAYwBoAH0APQBBAEUAXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAVwBlAHQAXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEUAXAAiACwAIABcACIAYQBuAG4AdQBhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABiAHkAIABlAGEAYwBoACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgAsACAAXAAiAGsAZwAgAE4ALwB5AGUAYQByAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABiAHkAIAA0AC4ANwAuADEALgAzACwAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBXAGUAdABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAbgBpAHQAcgBvAGcAZQBuACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHoAXAAiACwAIABcACIAbABvAGMAYQB0AGkAbwBuACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsACAAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUASABhAHIAdgBlAHMAdABJAG4AZABlAHgAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBEAGEAdABhACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0ACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbAAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADIAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFQAbwBQAGEAcwB0AHUAcgBlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADIAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFQAbwBQAGEAcwB0AHUAcgBlAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADIAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFQAbwBQAGEAcwB0AHUAcgBlAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -29392,7 +29406,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVQBOAEQAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgADAAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABpAHQAbABlAEMAZQBsAGwALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwALABcAG4AIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgATABFAEYAVAAoAFMAbwB1AHIAYwBlAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALABcACIALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwAKQAgAC0AMQApACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAXAAiACwAIABcACIAXAAiACkAIABcAHUAMAAwADIANgAgAFwAIgAgAFwAIgAgAFwAdQAwADAAMgA2ACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADEAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwB5AGUAYQByACkAIAAoAE0AagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABoAGUAYQBkACAALwAgAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBNAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAA2ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAANAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADIAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcAByAG8AZAB1AGMAZQBkACAAYgB5ACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAAVgBTAC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAFYAUwBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcAByAG8AZAB1AGMAZQBkACAAYgB5ACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAFYAUwAgAC8AIABoAGUAYQBkACAALwAgAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAyAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAXAAiACwAIABcACIAVgBTAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAbwBhAHQAcwBcACIALAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADAALgA5ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMgAuADcAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAwAC4AOQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADAALgAzADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMwA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAE4AMgBPAC8AaABlAGEAZAAvAHkAZQBhAHIAKQAgACgATgBFAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC8AIABoAGUAYQBkACAALwAgAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBOAEUAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAANwAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADEAMwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAzADkALgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAA3AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMQAzAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAA3AC4AMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADQAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AHMAIAAoAFcAYwBvACkAIAAoAGsAZwApACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAQQB2AGUAcgBhAGcAZQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBjAG8AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4ANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlACAAagBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADMAMwA2ACwAIABcACIALQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMwAzACwAIABcACIAMgA4AGsAZwAgAC0AIABsAG8AdwAgAHAAcgBvAGQAdQBjAHQAaQB2AGkAdAB5ACAAcwB5AHMAdABlAG0AcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMwAzACwAIABcACIANQAwAGsAZwAgAC0AIABoAGkAZwBoACAAcAByAG8AZAB1AGMAdABpAHYAaQB0AHkAIABzAHkAcwB0AGUAbQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMQAyADAALAAgADEAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAAMgAxADcALAAgADUANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIABcACIALQBcACIALAAgADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADMANwA3ACwAIAA1ADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAxADMAMAAsACAAMgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMQAyADAALAAgADEAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGUAcgBlAG4AYwBlAFwAIgAsACAAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAVABhAGIAbABlACAAMQAwAEEALgA1ACAAWwAyAF0AXAAiACwAIABcACIASQBQAEMAQwAgADIAMAAxADkAIABUAGEAYgBsAGUAIAAxADAALgAxADAAIABbADIAXQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADUAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0ATQBTAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADYAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHIAZQBnAGkAbwBuACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAcgBlAGcAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AQwBGAGkAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA2AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgBYADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgACgAbQAzACAAQwBIADQAIAAvACAAawBnACAAVgBTACkAIAAoAEIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIATwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuAFgAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAFQAaABlAHIAZQAgAHcAZQByAGUAIABuAG8AIAB2AGEAbAB1AGUAcwAgAGkAbgAgAFYARQBFAFIARwAgAHMAbwAgAHQAaABpAHMAIABkAGEAdABhACAAaABhAHMAIABiAGUAZQBuACAAZwBlAG4AZQByAGEAdABlAGQAIABiAHkAIAB1AHMAaQBuAGcAIABkAG8AYwB1AG0AZQBuAHQAZQBkACAAQgBPACAAdgBhAGwAdQBlAHMAIABmAHIAbwBtACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAEIATwBcACIALAAgAFwAIgBUAGEAawBlAG4AIABmAHIAbwBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMAAuADEAOQAsACAAXAAiAEYAZQBlAGQAbABvAHQALAAgAFAAYQBzAHQAdQByAGUAIABiAGUAZQBmAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAcABhAGMAYQBzAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAwAC4AMQA5ACwAIABcACIARgBlAGUAZABsAG8AdAAsACAAUABhAHMAdAB1AHIAZQAgAGIAZQBlAGYAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADAALgAzADYALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAALQAgAG0AZQBhAHQAIABjAGgAaQBjAGsAZQBuAHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAxACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA3ADoAIABNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAAtACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA3AC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAATQBhAG4AdQByAGUAIABNAGUAdABoAGEAbgBlACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAG8AZgAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAbgBFAF8AQwBIADQAXABuAHQAIABDAEgANABcAG4ARQBfAHsAQwBIADQAfQA9AFwAXABzAHUAbQBfAGoAXABcAHMAdQBtAF8AbQAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBtAFwAXAB0AGkAbQBlAHMAIAAzADYANQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBOAF8AagAgAD0AIABhAHYAZQByAGEAZwBlACAAYQBuAG4AdQBhAGwAIABuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIABqACAAKABoAGUAYQBkACkAXABuAE0AXwBqAG0AIAA9ACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAsACAATQBfAGoAbQAsAFwAbgAgACAAIAAgAFMAVQBNACgATgBfAGoAIAAqACAATQBfAGoAbQAgACoAIAAzADYANQApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAG8AZgAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADcALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAEgANAB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AbQAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBtAFwAXAB0AGkAbQBlAHMAIAAzADYANQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqAFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABhAG4AbgB1AGEAbAAgAG4AdQBtAGIAZQByACAAbwBmACAAbABpAHYAZQBzAHQAbwBjAGsAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAG0AXAAiACwAIABcACIAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANwAuADEALgAxACwAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAFwAIgAsACAAXAAiAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABcAG4AQQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAE0AXwBqAG0AXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AagBtAD0AVgBTAF8AagBcAFwAdABpAG0AZQBzACAAQgBfAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AbQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwBpAG0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcAG4AVgBTAF8AagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABrAGcALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4AQgBfAE8AIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAAoAG0AMwAgAEMASAA0AC8AawBnACAAVgBTACkAXABuAE0ATQBTAF8AbQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAIABpAG4AIABlAGEAYwBoACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXABuAE0AQwBGAF8AaQBtACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAawBnAC8AbQAzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAF8AagAsACAAQgBfAE8ALAAgAE0ATQBTAF8AbQAsACAATQBDAEYAXwBpAG0ALAAgAHIAaABvACwAXABuACAAIAAgACAAVgBTAF8AagAgACoAIABCAF8ATwAgACoAIABNAE0AUwBfAG0AIAAqACAATQBDAEYAXwBpAG0AIAAqACAAcgBoAG8AXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagBtAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAagBtAH0APQBWAFMAXwBqAFwAXAB0AGkAbQBlAHMAIABCAF8ATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwBtAFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALAAgAFwAIgB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAXwBPAFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBfAGkAbQBcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGUAIABhAG4AZAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsACAAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAGsAZwAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMAXwBqAFwAIgAsACAAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBfAE8AXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAXAAiACwAIABcACIAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlACAAaQBuACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAF8AaQBtAFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsACAAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAGsAZwAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgAsACAAXAAiAGQAZQBnAHIAZQBlAHMAIABDAGUAbABzAGkAdQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADcAOgAgAE0AYQBuAHUAcgBlACAATQBhAG4AYQBnAGUAbQBlAG4AdAAgAC0AIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADcALgAxAC4AMwAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABTAG8AaQBsACAARABpAHIAZQBjAHQAIABOADIATwAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABcAG4ARABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIABzAG8AaQBsAHMAIABmAHIAbwBtACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAHQAbwAgAHAAYQBzAHQAdQByAGUAXABuAEUAXwBOADIATwBkAGkAcgBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwAsAGQAaQByAH0APQBBAEUAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUABSAFAAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AQQBFACAAPQAgAGEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAATgAvAHkAZQBhAHIAKQBcAG4ARQBGAF8AUABSAFAAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIAB0AG8AIABzAG8AaQBsACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAZABlAHAAbwBzAGkAdABlAGQAKQBcAG4AQwBfAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAEUALAAgAEUARgBfAFAAUgBQACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIABBAEUAIAAqACAARQBGAF8AUABSAFAAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABhAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAHMAbwBpAGwAcwAgAGYAcgBvAG0AIABkAGUAcABvAHMAaQB0AGkAbwBuACAAbwBmACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAdABvACAAcABhAHMAdAB1AHIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAGQAaQByAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA3AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AQQBFAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFAAUgBQAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBFAFwAIgAsACAAXAAiAGEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AeQBlAGEAcgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA3AC4AMQAuADMALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBQAFIAUABcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGQAZQBwAG8AcwBpAHQAZQBkAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsACAAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB6AFwAIgAsACAAXAAiAHcAZQB0ACAAbwByACAAZAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXABuAEEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AG8AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXABuAEEARQBcAG4AawBnACAATgAvAHkAZQBhAHIAXABuAEEARQA9AFwAXABzAHUAbQBfAGoAKABOAF8AagBcAFwAdABpAG0AZQBzACAATgBFAF8AagBcAFwAdABpAG0AZQBzACAAMwA2ADUAKQBcAG4ATgBfAGoAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABsAGkAdgBlAHMAdABvAGMAawAgAG8AZgAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIABqACAAKABoAGUAYQBkACkAXABuAE4ARQBfAGoAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAIAAoAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAsACAATgBFAF8AagAsAFwAbgAgACAAIAAgAE4AXwBqACAAKgAgAE4ARQBfAGoAIAAqACAAMwA2ADUAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBuAG4AdQBhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABiAHkAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAbwAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAC8AeQBlAGEAcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADcALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADIAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFQAbwBQAGEAcwB0AHUAcgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABOAEUAXwBqAFwAXAB0AGkAbQBlAHMAIAAzADYANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAbwBmACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARQBfAGoAXAAiACwAIABcACIAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAXAAiACwAIABcACIAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADcAOgAgAE0AYQBuAHUAcgBlACAATQBhAG4AYQBnAGUAbQBlAG4AdAAgAC0AIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADcALgAxAC4ANQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABTAG8AaQBsACAAQQB0AG0AbwBzAHAAaABlAHIAaQBjACAARABlAHAAbwBzAGkAdABpAG8AbgAgAE4AMgBPACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFwAbgBBAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAbgBFAF8ATgAyAE8AYQBkAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPACwAYQBkAH0APQBNAF8AewB2AG8AbAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAE0AXwB2AG8AbAAgAD0AIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAF8ATgAyAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBfAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AdgBvAGwALAAgAEUARgBfAE4AMgBPACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIABNAF8AdgBvAGwAIAAqACAARQBGAF8ATgAyAE8AIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AYQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA3AC4AMQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABhAGQAfQA9AE0AXwB7AHYAbwBsAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AdgBvAGwAXAAiACwAIABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANwAuADEALgA1ACwAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgAyAE8AXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALAAgAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAXAAiACwAIABcACIAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBQAGEAcwB0AHUAcgBlAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUAXABuAE0AXwB2AG8AbABcAG4AawBnACAATgBcAG4ATQBfAHsAdgBvAGwAfQA9AEEARQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBHAEEAUwBNAHMAbwBpAGwAXABuAEEARQAgAD0AIABhAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAE4ALwB5AGUAYQByACkAXABuAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACAAKAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBFACwAIABGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbAAsAFwAbgAgACAAIAAgAEEARQAgACoAIABGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB2AG8AbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA3AC4AMQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AHYAbwBsAH0APQBBAEUAXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBFAFwAIgAsACAAXAAiAGEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AeQBlAGEAcgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAYgB5ACAANAAuADcALgAxAC4AMwAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANwA6ACAATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAALQAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANwAuADEALgA3ACAATQBlAHQAaABvAGQAIAAxACAALQAgAFMAbwBpAGwAIABMAGUAYQBjAGgAaQBuAGcAIABBAG4AZAAgAFIAdQBuAG8AZgBmACAATgAyAE8AIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFwAbgBMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAbgBFAF8ATgAyAE8AbABlAGEAYwBoAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPACwAbABlAGEAYwBoAH0APQBNAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATQBfAGwAZQBhAGMAaAAgAD0AIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAF8AbABlAGEAYwBoACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBsAGUAYQBjAGgALAAgAEUARgBfAGwAZQBhAGMAaAAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAATQBfAGwAZQBhAGMAaAAgACoAIABFAEYAXwBsAGUAYQBjAGgAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBsAGUAYQBjAGgAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADEALgA3ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABsAGUAYQBjAGgAfQA9AE0AXwB7AGwAZQBhAGMAaAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGwAZQBhAGMAaAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AbABlAGEAYwBoAFwAIgAsACAAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADcALgAxAC4ANwAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGwAZQBhAGMAaABcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsACAAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAE0AXwBsAGUAYQBjAGgAXABuAGsAZwAgAE4AXABuAE0AXwB7AGwAZQBhAGMAaAB9AD0AQQBFAFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAFcAZQB0AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEwARQBBAEMASABcAG4AQQBFACAAPQAgAGEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAATgAvAHkAZQBhAHIAKQBcAG4ARgByAGEAYwBXAGUAdAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ARgByAGEAYwBMAEUAQQBDAEgAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBsAGwAIABuAGkAdAByAG8AZwBlAG4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEARQAsACAARgByAGEAYwBXAGUAdAAsACAARgByAGEAYwBMAEUAQQBDAEgALABcAG4AIAAgACAAIABBAEUAIAAqACAARgByAGEAYwBXAGUAdAAgACoAIABGAHIAYQBjAEwARQBBAEMASABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AbABlAGEAYwBoAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA3AC4AMQAuADcALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBsAGUAYQBjAGgAfQA9AEEARQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBXAGUAdABcAFwAdABpAG0AZQBzACAARgByAGEAYwBMAEUAQQBDAEgAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARQBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACwAIABcACIAawBnACAATgAvAHkAZQBhAHIAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGIAeQAgADQALgA3AC4AMQAuADMALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAFcAZQB0AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBsAGwAIABuAGkAdAByAG8AZwBlAG4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgBsAG8AYwBhAHQAaQBvAG4AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAEQAYQB0AGEAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADIAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFQAbwBQAGEAcwB0AHUAcgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADIAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFQAbwBQAGEAcwB0AHUAcgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -29403,23 +29429,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -29436,4 +29446,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/4_7_ManureManagement_OtherLivestock_WIP_v01.prename.bak.xlsx
+++ b/Excel/4_7_ManureManagement_OtherLivestock_WIP_v01.prename.bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC90442-0B3A-4D2C-9068-B004843A827A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03255E2-E9AA-48AD-A2C6-A6B9C2325E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" firstSheet="8" activeTab="11" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" firstSheet="8" activeTab="11" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -27,9 +27,6 @@
     <sheet name="Constants - Common" sheetId="106" r:id="rId12"/>
     <sheet name="Acknowledgements" sheetId="72" r:id="rId13"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId14"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -45,7 +42,17 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray,
+    _xlfn.XLOOKUP(
+        MEDIAN(
+            ROUND(_xlpm.Temperature, 0),
+            MIN(_xlpm.TemperatureArray),
+            MAX(_xlpm.TemperatureArray)
+        ),
+        _xlpm.TemperatureArray,
+        _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)
+    )
+)</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
@@ -61,9 +68,28 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse,
+    IFERROR(
+        _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1,
+            _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)
+        ),
+        IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)
+    )
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse,
+    _xlfn.XLOOKUP(1, (_xlpm.LookupArray1=_xlpm.LookupValue1)*(_xlpm.LookupArray2=_xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse))
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell,
+    SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) -1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell,
+  _xlfn.LET(
+    _xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"),
+    _xlpm.addr, CELL("address", _xlpm.TargetCell),
+    "#" &amp; _xlpm.addr
+  )
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -228,6 +254,61 @@
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Title">_xlfn.LAMBDA("Table 5.12 Additional symbols used in algorithms for manure related emissions")</definedName>
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Vairable">_xlfn.LAMBDA("MMS")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(9, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Product","Source region";"Cattle, for manufacturing beef","Australia";"Cattle, for prime beef","NSW";"Cattle, weaners","NT";"","QLD";"","SA";"","TAS";"","VIC";"","WA"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Title">_xlfn.LAMBDA("Beef cattle products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(2, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Product","Source region";"Chickens","Australia"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Title">_xlfn.LAMBDA("Chickens products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(2, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Product","Source region";"Dairy cows","VIC"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Title">_xlfn.LAMBDA("Dairy cattle products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(2, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Product","Source region";"Pigs","Australia"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Title">_xlfn.LAMBDA("Pigs products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(8, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Product","Source region";"Sheep, for mutton","Australia";"Sheep, for prime lamb","NSW";"","QLD";"","SA";"","TAS";"","VIC";"","WA"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Title">_xlfn.LAMBDA("Sheep products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Vairable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Fertiliser_Equations_InorganicCO2.VEERG_5_1_1_3__2_MassOfUreaInInorganicFertiliser_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"TM_jf","total mass of inorganic fertiliser type f applied to production system j : kg","Input";"FU_f","fraction of urea in fertiliser type f : kg urea/kg","Lookup"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Inoput_Cell_Livestock_antibiotics">#REF!</definedName>
@@ -339,7 +420,13 @@
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Unit">_xlfn.LAMBDA("fraction")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Variable">_xlfn.LAMBDA("MMSm")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State","Pasture range and paddock","Uncovered Anaerobic lagoon";"ACT",0.0047,0.71;"NSW",0.0047,0.75;"NT",0.0047,0.8;"QLD",0.0047,0.78;"SA",0.0047,0.74;"TAS",0.0047,0.7;"VIC",0.0047,0.74;"WA",0.0047,0.76}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(9, 3,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"State","Pasture range and paddock","Uncovered Anaerobic lagoon";"ACT",0.0047,0.71;"NSW",0.0047,0.75;"NT",0.0047,0.8;"QLD",0.0047,0.78;"SA",0.0047,0.74;"TAS",0.0047,0.7;"VIC",0.0047,0.74;"WA",0.0047,0.76}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.5.6")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Title">_xlfn.LAMBDA("Other Livestock - Methane conversion factor per region")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Unit">_xlfn.LAMBDA("fraction")</definedName>
@@ -351,7 +438,13 @@
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Unit">_xlfn.LAMBDA("m3 CH4 / kg VS")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Variable">_xlfn.LAMBDA("BO")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: There were no values in VEERG so this data has been generated by using documented BO values from other livestock")</definedName>
-    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Other Livestock Type","NEj";"Buffalo",39.5;"Goats",7;"Deer",13.2;"Camels",39.5;"Alpacas",7;"Horses",39.5;"Mules/asses",13.2;"Emus/ostriches",7}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(9, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Other Livestock Type","NEj";"Buffalo",39.5;"Goats",7;"Deer",13.2;"Camels",39.5;"Alpacas",7;"Horses",39.5;"Mules/asses",13.2;"Emus/ostriches",7}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.5.3")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Title">_xlfn.LAMBDA("Other Livestock - Nitrogen excreted per livestock type")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Unit">_xlfn.LAMBDA("kg N2O / head / year")</definedName>
@@ -9275,26 +9368,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -9369,7 +9442,7 @@
     <tableColumn id="1" xr3:uid="{C1BE61FE-4062-42B2-A2C3-5D1021EC5783}" name="Other livestock type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{068A837D-7F3F-459D-A755-48E9682BAEAC}" name="Mj" dataDxfId="58" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{068A837D-7F3F-459D-A755-48E9682BAEAC}" name="Mj" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9507,49 +9580,49 @@
     <tableColumn id="1" xr3:uid="{1F756ECE-8D0E-46EB-AA15-851322033D31}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E4E36567-BBA2-4402-A05A-770FAF31C38A}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{E4E36567-BBA2-4402-A05A-770FAF31C38A}" name="MAT" totalsRowDxfId="58" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D6E8900F-E2A4-4F43-862C-139252D3337C}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{D6E8900F-E2A4-4F43-862C-139252D3337C}" name="MAP" totalsRowDxfId="57" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4BAD5116-B162-449C-8438-48EE46F623C9}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{4BAD5116-B162-449C-8438-48EE46F623C9}" name="Frost days per year" totalsRowDxfId="56" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{E3DBB9F9-9030-4FF2-93F7-1046C63305FF}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{E3DBB9F9-9030-4FF2-93F7-1046C63305FF}" name="Elevation" totalsRowDxfId="55" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D19E1AF7-C103-4465-827A-272966E9BB2B}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{D19E1AF7-C103-4465-827A-272966E9BB2B}" name="MAP:PET" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{5C718C43-26C6-43E1-B01C-9B8888AF5CD7}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{5C718C43-26C6-43E1-B01C-9B8888AF5CD7}" name="Min temp" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{3F0FA349-758F-440D-8B9F-92BEDB006B3B}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{3F0FA349-758F-440D-8B9F-92BEDB006B3B}" name="Max temp" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6FE4C191-1D7C-447A-807F-52BAA1F83C1B}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{6FE4C191-1D7C-447A-807F-52BAA1F83C1B}" name="Min rainfall" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C465259B-535A-4418-9C56-99040421033F}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{C465259B-535A-4418-9C56-99040421033F}" name="Max rainfall" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{049DB580-CA31-478D-A316-B9826DC5976C}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{049DB580-CA31-478D-A316-B9826DC5976C}" name="Min frost days" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E28D5CDC-6CDE-40AC-BB69-B520E6BE9ECE}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{E28D5CDC-6CDE-40AC-BB69-B520E6BE9ECE}" name="Max frost days" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{28DEE6A7-2DC0-4DF3-BA96-82E0B5206A88}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{28DEE6A7-2DC0-4DF3-BA96-82E0B5206A88}" name="Min elevation" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{3CEAC3FE-E190-4B17-A0E5-E93072D2EE0C}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{3CEAC3FE-E190-4B17-A0E5-E93072D2EE0C}" name="Max elevation" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{B2607A8A-4828-4A7F-8B59-AFDF70121EA9}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{B2607A8A-4828-4A7F-8B59-AFDF70121EA9}" name="Min MAP:PET" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{EE9AE32D-CD32-49F5-8434-FED04B1C7173}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{EE9AE32D-CD32-49F5-8434-FED04B1C7173}" name="Max MAP:PET" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9567,7 +9640,7 @@
     <tableColumn id="1" xr3:uid="{FC589081-50C7-4011-B899-F7D6142FB1B3}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B9257959-AB83-4C24-830F-528097C2CA9C}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{B9257959-AB83-4C24-830F-528097C2CA9C}" name="Wet or Dry Zone" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9646,16 +9719,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{50599DA1-A8E6-43AC-9BA5-F5F05D972680}" name="Table_SourceData_OtherLivestock_VolatileSolids" displayName="Table_SourceData_OtherLivestock_VolatileSolids" ref="D24:E32" totalsRowShown="0" dataDxfId="57" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{50599DA1-A8E6-43AC-9BA5-F5F05D972680}" name="Table_SourceData_OtherLivestock_VolatileSolids" displayName="Table_SourceData_OtherLivestock_VolatileSolids" ref="D24:E32" totalsRowShown="0" dataDxfId="21" dataCellStyle="Content normal">
   <autoFilter ref="D24:E32" xr:uid="{50599DA1-A8E6-43AC-9BA5-F5F05D972680}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{224F01F5-9F04-424C-9B4C-94B1D666F42B}" name="Other livestock type" dataDxfId="56" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{224F01F5-9F04-424C-9B4C-94B1D666F42B}" name="Other livestock type" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D62AC0D1-1095-4EC7-994A-E2C80051C1F2}" name="VSj" dataDxfId="55" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D62AC0D1-1095-4EC7-994A-E2C80051C1F2}" name="VSj" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9691,7 +9764,7 @@
     <tableColumn id="1" xr3:uid="{42786E11-D892-4920-9A89-7DF8F5B57ECD}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F8ACB435-9333-46C3-9CE1-E917C7F45FDD}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{F8ACB435-9333-46C3-9CE1-E917C7F45FDD}" name="FracWET" dataDxfId="42">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9739,7 +9812,7 @@
     <tableColumn id="1" xr3:uid="{1CA22ABA-FF81-4B2A-8F64-49727B4BF401}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{06CFAD91-F13C-4026-9DDC-82944352DBB0}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{06CFAD91-F13C-4026-9DDC-82944352DBB0}" name="FracWET" dataDxfId="41" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9757,7 +9830,7 @@
     <tableColumn id="1" xr3:uid="{ADFFE3A2-3C8A-4121-B340-0E2214EC5BA1}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2C8D4993-4AE2-4BA6-861D-7C75168C934E}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2C8D4993-4AE2-4BA6-861D-7C75168C934E}" name="EFPRP" dataDxfId="40" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9775,7 +9848,7 @@
     <tableColumn id="1" xr3:uid="{557AFE4A-E50B-48C4-A78F-EDB3E2F5513D}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2B6FAA2C-6699-4E65-8AF4-7FFB022E013A}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2B6FAA2C-6699-4E65-8AF4-7FFB022E013A}" name="Season" dataDxfId="39" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9807,49 +9880,49 @@
     <tableColumn id="1" xr3:uid="{5BE488E9-C88F-4D40-BFE4-2F14BFE204FE}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7471337B-A383-48F1-9140-7A247CE94C8C}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{7471337B-A383-48F1-9140-7A247CE94C8C}" name="MAT (ºC)" dataDxfId="38" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9751CF7A-2A90-41C3-B0C7-75B6BE4418D9}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9751CF7A-2A90-41C3-B0C7-75B6BE4418D9}" name="Anaerobic lagoon" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CA5FACFF-2A01-4823-AE11-C25A5DB63212}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{CA5FACFF-2A01-4823-AE11-C25A5DB63212}" name="Digester / covered lagoons" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{AD3B111E-1B73-4EAA-ACFB-B1EA17DB2261}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{AD3B111E-1B73-4EAA-ACFB-B1EA17DB2261}" name="Liquid systems" dataDxfId="35" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{47E6E961-631F-4462-83C1-CBA267F81DBF}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{47E6E961-631F-4462-83C1-CBA267F81DBF}" name="Daily spread" dataDxfId="34" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{5E5FC724-F551-44A5-B89F-454716A00746}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{5E5FC724-F551-44A5-B89F-454716A00746}" name="Composting (passive windrow)" dataDxfId="33" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{94DCCEDE-8F03-4DCB-BD73-4137AA6BFB7B}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{94DCCEDE-8F03-4DCB-BD73-4137AA6BFB7B}" name="Solid storage" dataDxfId="32" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{D2CE3558-5412-4654-9F72-DA1821CDE596}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{D2CE3558-5412-4654-9F72-DA1821CDE596}" name="Pit storage" dataDxfId="31" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{607A79A9-61FE-48BF-BE48-0965C1DF8C73}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{607A79A9-61FE-48BF-BE48-0965C1DF8C73}" name="Deep litter" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{98F5211C-781C-45BD-AF95-05B148C528F9}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{98F5211C-781C-45BD-AF95-05B148C528F9}" name="Poultry manure with bedding" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{154A1334-E483-46FC-9EFD-C7408471DC4C}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{154A1334-E483-46FC-9EFD-C7408471DC4C}" name="Poultry manure without bedding" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{CB4AF493-91F1-476F-AA2D-085C994C3162}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{CB4AF493-91F1-476F-AA2D-085C994C3162}" name="Direct processing" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{6D0E7416-BFEB-44E9-8544-61035BEA7B24}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{6D0E7416-BFEB-44E9-8544-61035BEA7B24}" name="Direct application" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{7CBEB24B-DEDB-4F2B-B7E6-E6997FA2618D}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{7CBEB24B-DEDB-4F2B-B7E6-E6997FA2618D}" name="Pasture range and paddock" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{4F278C8D-7F75-44BF-809F-EC6F8B2D6E58}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{4F278C8D-7F75-44BF-809F-EC6F8B2D6E58}" name="MAT raw" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9867,7 +9940,7 @@
     <tableColumn id="1" xr3:uid="{1512BED0-98D7-41FD-B812-44719FDE3EC4}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{73340C7C-6E56-43EB-8AAB-D3E271491791}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{73340C7C-6E56-43EB-8AAB-D3E271491791}" name="EFNi &amp; EFN2Oi" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9876,16 +9949,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EFDE3B07-3717-4AE7-8210-BEB8FBB5C09A}" name="Table_SourceData_OtherLivestock_NitrogenExcreted" displayName="Table_SourceData_OtherLivestock_NitrogenExcreted" ref="D39:E47" totalsRowShown="0" dataDxfId="54" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EFDE3B07-3717-4AE7-8210-BEB8FBB5C09A}" name="Table_SourceData_OtherLivestock_NitrogenExcreted" displayName="Table_SourceData_OtherLivestock_NitrogenExcreted" ref="D39:E47" totalsRowShown="0" dataDxfId="18" dataCellStyle="Content normal">
   <autoFilter ref="D39:E47" xr:uid="{EFDE3B07-3717-4AE7-8210-BEB8FBB5C09A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{99F8CB88-8A74-44CD-B1D3-22D4849941C6}" name="Other livestock type" dataDxfId="53" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{99F8CB88-8A74-44CD-B1D3-22D4849941C6}" name="Other livestock type" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CD5FC568-A825-4281-84C4-C2307E67DC49}" name="NEj" dataDxfId="52" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{CD5FC568-A825-4281-84C4-C2307E67DC49}" name="NEj" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9894,20 +9967,20 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7551F12E-AA31-4EE1-8F93-A397BC98EF70}" name="Table_SourceData_OtherLivestock_AverageLiveweight" displayName="Table_SourceData_OtherLivestock_AverageLiveweight" ref="D54:F64" totalsRowShown="0" dataDxfId="51" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7551F12E-AA31-4EE1-8F93-A397BC98EF70}" name="Table_SourceData_OtherLivestock_AverageLiveweight" displayName="Table_SourceData_OtherLivestock_AverageLiveweight" ref="D54:F64" totalsRowShown="0" dataDxfId="15" dataCellStyle="Content normal">
   <autoFilter ref="D54:F64" xr:uid="{7551F12E-AA31-4EE1-8F93-A397BC98EF70}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{816644D3-41EE-45F6-A3CE-CACB3EB69547}" name="Other livestock type" dataDxfId="50" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{816644D3-41EE-45F6-A3CE-CACB3EB69547}" name="Other livestock type" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{53512804-9E08-42E2-B55E-1C89A4C09FEE}" name="Wco" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{53512804-9E08-42E2-B55E-1C89A4C09FEE}" name="Wco" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0BB31A55-829C-489B-82D5-5810EC5F02C8}" name="Wco2" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{0BB31A55-829C-489B-82D5-5810EC5F02C8}" name="Wco2" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9916,20 +9989,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9A69C610-A352-421F-BE36-E6EDDE86179E}" name="Table_SourceData_OtherLivestock_FractionWasteInMMS" displayName="Table_SourceData_OtherLivestock_FractionWasteInMMS" ref="D71:F79" totalsRowShown="0" dataDxfId="47" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9A69C610-A352-421F-BE36-E6EDDE86179E}" name="Table_SourceData_OtherLivestock_FractionWasteInMMS" displayName="Table_SourceData_OtherLivestock_FractionWasteInMMS" ref="D71:F79" totalsRowShown="0" dataDxfId="11" dataCellStyle="Content normal">
   <autoFilter ref="D71:F79" xr:uid="{9A69C610-A352-421F-BE36-E6EDDE86179E}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A6CB9AC6-F6CE-49B7-A982-F82076716CA3}" name="Other livestock type" dataDxfId="46" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{A6CB9AC6-F6CE-49B7-A982-F82076716CA3}" name="Other livestock type" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8AFBE1CB-9936-4A35-A761-4DCB7B6BA889}" name="Pasture range and paddock" dataDxfId="45" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8AFBE1CB-9936-4A35-A761-4DCB7B6BA889}" name="Pasture range and paddock" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{95A534B1-6D18-468E-ACD4-CB91F74DE859}" name="Uncovered anaerobic lagoon" dataDxfId="44" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{95A534B1-6D18-468E-ACD4-CB91F74DE859}" name="Uncovered anaerobic lagoon" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9938,20 +10011,20 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{5A098EC4-878C-4F1B-9A39-76DE07EA3C35}" name="Table_SourceData_OtherLivestock_MCF" displayName="Table_SourceData_OtherLivestock_MCF" ref="D86:F94" totalsRowShown="0" dataDxfId="43" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{5A098EC4-878C-4F1B-9A39-76DE07EA3C35}" name="Table_SourceData_OtherLivestock_MCF" displayName="Table_SourceData_OtherLivestock_MCF" ref="D86:F94" totalsRowShown="0" dataDxfId="7" dataCellStyle="Content normal">
   <autoFilter ref="D86:F94" xr:uid="{5A098EC4-878C-4F1B-9A39-76DE07EA3C35}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8D99AA70-8F55-4D11-BC0B-A089B4E9846C}" name="Other livestock type" dataDxfId="42" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{8D99AA70-8F55-4D11-BC0B-A089B4E9846C}" name="Other livestock type" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8669BCCE-EDA0-482F-B818-E7495ADAD605}" name="Pasture range and paddock" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8669BCCE-EDA0-482F-B818-E7495ADAD605}" name="Pasture range and paddock" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F18CF34C-B873-434B-8D03-00492CEC1FC6}" name="Uncovered anaerobic lagoon" dataDxfId="40" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{F18CF34C-B873-434B-8D03-00492CEC1FC6}" name="Uncovered anaerobic lagoon" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9960,20 +10033,20 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{B8FC34BB-AAD9-4D2A-8283-00CB77181C08}" name="Table_SourceData_OtherLivestock_MethaneEmissionsPotential" displayName="Table_SourceData_OtherLivestock_MethaneEmissionsPotential" ref="D102:F110" totalsRowShown="0" dataDxfId="39" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{B8FC34BB-AAD9-4D2A-8283-00CB77181C08}" name="Table_SourceData_OtherLivestock_MethaneEmissionsPotential" displayName="Table_SourceData_OtherLivestock_MethaneEmissionsPotential" ref="D102:F110" totalsRowShown="0" dataDxfId="3" dataCellStyle="Content normal">
   <autoFilter ref="D102:F110" xr:uid="{B8FC34BB-AAD9-4D2A-8283-00CB77181C08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{5720D920-9C04-4E20-8D42-759F7E36C7D8}" name="Other livestock type" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{5720D920-9C04-4E20-8D42-759F7E36C7D8}" name="Other livestock type" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Data(),Table_SourceData_OtherLivestock_MethaneEmissionsPotential[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E9A32AB0-4663-4816-913A-79DAAFF08391}" name="BO" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E9A32AB0-4663-4816-913A-79DAAFF08391}" name="BO" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Data(),Table_SourceData_OtherLivestock_MethaneEmissionsPotential[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{35962C17-3057-4CB9-8C5C-BED1CCB209DC}" name="Taken from" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{35962C17-3057-4CB9-8C5C-BED1CCB209DC}" name="Taken from" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Data(),Table_SourceData_OtherLivestock_MethaneEmissionsPotential[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -29192,26 +29265,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -29406,30 +29459,31 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVQBOAEQAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgADAAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABpAHQAbABlAEMAZQBsAGwALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwALABcAG4AIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgATABFAEYAVAAoAFMAbwB1AHIAYwBlAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALABcACIALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwAKQAgAC0AMQApACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAXAAiACwAIABcACIAXAAiACkAIABcAHUAMAAwADIANgAgAFwAIgAgAFwAIgAgAFwAdQAwADAAMgA2ACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADEAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwB5AGUAYQByACkAIAAoAE0AagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABoAGUAYQBkACAALwAgAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBNAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAA2ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAANAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADIAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcAByAG8AZAB1AGMAZQBkACAAYgB5ACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAAVgBTAC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAFYAUwBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcAByAG8AZAB1AGMAZQBkACAAYgB5ACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAFYAUwAgAC8AIABoAGUAYQBkACAALwAgAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAyAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAXAAiACwAIABcACIAVgBTAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAbwBhAHQAcwBcACIALAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADAALgA5ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMgAuADcAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAwAC4AOQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADAALgAzADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMwA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAE4AMgBPAC8AaABlAGEAZAAvAHkAZQBhAHIAKQAgACgATgBFAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC8AIABoAGUAYQBkACAALwAgAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBOAEUAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAANwAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADEAMwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAzADkALgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAA3AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMQAzAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAA3AC4AMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADQAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AHMAIAAoAFcAYwBvACkAIAAoAGsAZwApACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAQQB2AGUAcgBhAGcAZQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBjAG8AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4ANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlACAAagBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADMAMwA2ACwAIABcACIALQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMwAzACwAIABcACIAMgA4AGsAZwAgAC0AIABsAG8AdwAgAHAAcgBvAGQAdQBjAHQAaQB2AGkAdAB5ACAAcwB5AHMAdABlAG0AcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMwAzACwAIABcACIANQAwAGsAZwAgAC0AIABoAGkAZwBoACAAcAByAG8AZAB1AGMAdABpAHYAaQB0AHkAIABzAHkAcwB0AGUAbQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMQAyADAALAAgADEAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAAMgAxADcALAAgADUANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIABcACIALQBcACIALAAgADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADMANwA3ACwAIAA1ADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAxADMAMAAsACAAMgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMQAyADAALAAgADEAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGUAcgBlAG4AYwBlAFwAIgAsACAAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAVABhAGIAbABlACAAMQAwAEEALgA1ACAAWwAyAF0AXAAiACwAIABcACIASQBQAEMAQwAgADIAMAAxADkAIABUAGEAYgBsAGUAIAAxADAALgAxADAAIABbADIAXQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADUAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0ATQBTAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADYAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHIAZQBnAGkAbwBuACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAcgBlAGcAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AQwBGAGkAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA2AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgBYADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgACgAbQAzACAAQwBIADQAIAAvACAAawBnACAAVgBTACkAIAAoAEIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIATwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuAFgAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAFQAaABlAHIAZQAgAHcAZQByAGUAIABuAG8AIAB2AGEAbAB1AGUAcwAgAGkAbgAgAFYARQBFAFIARwAgAHMAbwAgAHQAaABpAHMAIABkAGEAdABhACAAaABhAHMAIABiAGUAZQBuACAAZwBlAG4AZQByAGEAdABlAGQAIABiAHkAIAB1AHMAaQBuAGcAIABkAG8AYwB1AG0AZQBuAHQAZQBkACAAQgBPACAAdgBhAGwAdQBlAHMAIABmAHIAbwBtACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAEIATwBcACIALAAgAFwAIgBUAGEAawBlAG4AIABmAHIAbwBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMAAuADEAOQAsACAAXAAiAEYAZQBlAGQAbABvAHQALAAgAFAAYQBzAHQAdQByAGUAIABiAGUAZQBmAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAcABhAGMAYQBzAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAwAC4AMQA5ACwAIABcACIARgBlAGUAZABsAG8AdAAsACAAUABhAHMAdAB1AHIAZQAgAGIAZQBlAGYAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADAALgAzADYALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAALQAgAG0AZQBhAHQAIABjAGgAaQBjAGsAZQBuAHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAxACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA3ADoAIABNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAAtACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA3AC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAATQBhAG4AdQByAGUAIABNAGUAdABoAGEAbgBlACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAG8AZgAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAbgBFAF8AQwBIADQAXABuAHQAIABDAEgANABcAG4ARQBfAHsAQwBIADQAfQA9AFwAXABzAHUAbQBfAGoAXABcAHMAdQBtAF8AbQAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBtAFwAXAB0AGkAbQBlAHMAIAAzADYANQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBOAF8AagAgAD0AIABhAHYAZQByAGEAZwBlACAAYQBuAG4AdQBhAGwAIABuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIABqACAAKABoAGUAYQBkACkAXABuAE0AXwBqAG0AIAA9ACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAsACAATQBfAGoAbQAsAFwAbgAgACAAIAAgAFMAVQBNACgATgBfAGoAIAAqACAATQBfAGoAbQAgACoAIAAzADYANQApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAG8AZgAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADcALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAEgANAB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AbQAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBtAFwAXAB0AGkAbQBlAHMAIAAzADYANQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqAFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABhAG4AbgB1AGEAbAAgAG4AdQBtAGIAZQByACAAbwBmACAAbABpAHYAZQBzAHQAbwBjAGsAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAG0AXAAiACwAIABcACIAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANwAuADEALgAxACwAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAFwAIgAsACAAXAAiAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABcAG4AQQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAE0AXwBqAG0AXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AagBtAD0AVgBTAF8AagBcAFwAdABpAG0AZQBzACAAQgBfAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AbQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwBpAG0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcAG4AVgBTAF8AagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABrAGcALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4AQgBfAE8AIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAAoAG0AMwAgAEMASAA0AC8AawBnACAAVgBTACkAXABuAE0ATQBTAF8AbQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAIABpAG4AIABlAGEAYwBoACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXABuAE0AQwBGAF8AaQBtACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAawBnAC8AbQAzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAF8AagAsACAAQgBfAE8ALAAgAE0ATQBTAF8AbQAsACAATQBDAEYAXwBpAG0ALAAgAHIAaABvACwAXABuACAAIAAgACAAVgBTAF8AagAgACoAIABCAF8ATwAgACoAIABNAE0AUwBfAG0AIAAqACAATQBDAEYAXwBpAG0AIAAqACAAcgBoAG8AXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagBtAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAagBtAH0APQBWAFMAXwBqAFwAXAB0AGkAbQBlAHMAIABCAF8ATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwBtAFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALAAgAFwAIgB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAXwBPAFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBfAGkAbQBcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGUAIABhAG4AZAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsACAAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAGsAZwAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMAXwBqAFwAIgAsACAAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBfAE8AXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAXAAiACwAIABcACIAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlACAAaQBuACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAF8AaQBtAFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsACAAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAGsAZwAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgAsACAAXAAiAGQAZQBnAHIAZQBlAHMAIABDAGUAbABzAGkAdQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADcAOgAgAE0AYQBuAHUAcgBlACAATQBhAG4AYQBnAGUAbQBlAG4AdAAgAC0AIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADcALgAxAC4AMwAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABTAG8AaQBsACAARABpAHIAZQBjAHQAIABOADIATwAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABcAG4ARABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIABzAG8AaQBsAHMAIABmAHIAbwBtACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAHQAbwAgAHAAYQBzAHQAdQByAGUAXABuAEUAXwBOADIATwBkAGkAcgBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwAsAGQAaQByAH0APQBBAEUAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUABSAFAAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AQQBFACAAPQAgAGEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAATgAvAHkAZQBhAHIAKQBcAG4ARQBGAF8AUABSAFAAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIAB0AG8AIABzAG8AaQBsACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAZABlAHAAbwBzAGkAdABlAGQAKQBcAG4AQwBfAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAEUALAAgAEUARgBfAFAAUgBQACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIABBAEUAIAAqACAARQBGAF8AUABSAFAAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABhAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAHMAbwBpAGwAcwAgAGYAcgBvAG0AIABkAGUAcABvAHMAaQB0AGkAbwBuACAAbwBmACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAdABvACAAcABhAHMAdAB1AHIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAGQAaQByAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA3AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AQQBFAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFAAUgBQAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBFAFwAIgAsACAAXAAiAGEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AeQBlAGEAcgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgA3AC4AMQAuADMALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBQAFIAUABcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGQAZQBwAG8AcwBpAHQAZQBkAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsACAAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB6AFwAIgAsACAAXAAiAHcAZQB0ACAAbwByACAAZAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXABuAEEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AG8AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXABuAEEARQBcAG4AawBnACAATgAvAHkAZQBhAHIAXABuAEEARQA9AFwAXABzAHUAbQBfAGoAKABOAF8AagBcAFwAdABpAG0AZQBzACAATgBFAF8AagBcAFwAdABpAG0AZQBzACAAMwA2ADUAKQBcAG4ATgBfAGoAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABsAGkAdgBlAHMAdABvAGMAawAgAG8AZgAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIABqACAAKABoAGUAYQBkACkAXABuAE4ARQBfAGoAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAIAAoAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAsACAATgBFAF8AagAsAFwAbgAgACAAIAAgAE4AXwBqACAAKgAgAE4ARQBfAGoAIAAqACAAMwA2ADUAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBuAG4AdQBhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABiAHkAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAbwAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAC8AeQBlAGEAcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADcALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADIAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFQAbwBQAGEAcwB0AHUAcgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABOAEUAXwBqAFwAXAB0AGkAbQBlAHMAIAAzADYANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAbwBmACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARQBfAGoAXAAiACwAIABcACIAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAXAAiACwAIABcACIAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADcAOgAgAE0AYQBuAHUAcgBlACAATQBhAG4AYQBnAGUAbQBlAG4AdAAgAC0AIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADcALgAxAC4ANQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABTAG8AaQBsACAAQQB0AG0AbwBzAHAAaABlAHIAaQBjACAARABlAHAAbwBzAGkAdABpAG8AbgAgAE4AMgBPACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFwAbgBBAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAbgBFAF8ATgAyAE8AYQBkAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPACwAYQBkAH0APQBNAF8AewB2AG8AbAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAE0AXwB2AG8AbAAgAD0AIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAF8ATgAyAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBfAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AdgBvAGwALAAgAEUARgBfAE4AMgBPACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIABNAF8AdgBvAGwAIAAqACAARQBGAF8ATgAyAE8AIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AYQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA3AC4AMQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABhAGQAfQA9AE0AXwB7AHYAbwBsAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AdgBvAGwAXAAiACwAIABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4ANwAuADEALgA1ACwAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgAyAE8AXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALAAgAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAXAAiACwAIABcACIAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBQAGEAcwB0AHUAcgBlAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUAXABuAE0AXwB2AG8AbABcAG4AawBnACAATgBcAG4ATQBfAHsAdgBvAGwAfQA9AEEARQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBHAEEAUwBNAHMAbwBpAGwAXABuAEEARQAgAD0AIABhAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAE4ALwB5AGUAYQByACkAXABuAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACAAKAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBFACwAIABGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbAAsAFwAbgAgACAAIAAgAEEARQAgACoAIABGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB2AG8AbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA3AC4AMQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AHYAbwBsAH0APQBBAEUAXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBFAFwAIgAsACAAXAAiAGEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AeQBlAGEAcgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAYgB5ACAANAAuADcALgAxAC4AMwAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANwA6ACAATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAALQAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANwAuADEALgA3ACAATQBlAHQAaABvAGQAIAAxACAALQAgAFMAbwBpAGwAIABMAGUAYQBjAGgAaQBuAGcAIABBAG4AZAAgAFIAdQBuAG8AZgBmACAATgAyAE8AIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFwAbgBMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAbgBFAF8ATgAyAE8AbABlAGEAYwBoAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPACwAbABlAGEAYwBoAH0APQBNAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATQBfAGwAZQBhAGMAaAAgAD0AIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAF8AbABlAGEAYwBoACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBsAGUAYQBjAGgALAAgAEUARgBfAGwAZQBhAGMAaAAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAATQBfAGwAZQBhAGMAaAAgACoAIABFAEYAXwBsAGUAYQBjAGgAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBsAGUAYQBjAGgAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADEALgA3ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABsAGUAYQBjAGgAfQA9AE0AXwB7AGwAZQBhAGMAaAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGwAZQBhAGMAaAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AbABlAGEAYwBoAFwAIgAsACAAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADcALgAxAC4ANwAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGwAZQBhAGMAaABcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsACAAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAE0AXwBsAGUAYQBjAGgAXABuAGsAZwAgAE4AXABuAE0AXwB7AGwAZQBhAGMAaAB9AD0AQQBFAFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAFcAZQB0AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEwARQBBAEMASABcAG4AQQBFACAAPQAgAGEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAATgAvAHkAZQBhAHIAKQBcAG4ARgByAGEAYwBXAGUAdAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ARgByAGEAYwBMAEUAQQBDAEgAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBsAGwAIABuAGkAdAByAG8AZwBlAG4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEARQAsACAARgByAGEAYwBXAGUAdAAsACAARgByAGEAYwBMAEUAQQBDAEgALABcAG4AIAAgACAAIABBAEUAIAAqACAARgByAGEAYwBXAGUAdAAgACoAIABGAHIAYQBjAEwARQBBAEMASABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AbABlAGEAYwBoAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA3AC4AMQAuADcALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBsAGUAYQBjAGgAfQA9AEEARQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBXAGUAdABcAFwAdABpAG0AZQBzACAARgByAGEAYwBMAEUAQQBDAEgAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARQBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACwAIABcACIAawBnACAATgAvAHkAZQBhAHIAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGIAeQAgADQALgA3AC4AMQAuADMALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAFcAZQB0AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBsAGwAIABuAGkAdAByAG8AZwBlAG4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgBsAG8AYwBhAHQAaQBvAG4AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAEQAYQB0AGEAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADEAXwBfADIAXwBBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAxAF8AXwAyAF8AQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMQBfAF8AMgBfAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAxAF8ARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AaQBsAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADEAXwBEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBpAGwAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMQBfAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGkAbABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADIAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFQAbwBQAGEAcwB0AHUAcgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAE4AMgBPAEQAaQByAGUAYwB0AC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8AMwBfAF8AMgBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAVABvAFAAYQBzAHQAdQByAGUAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBOADIATwBEAGkAcgBlAGMAdAAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADMAXwBfADIAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFQAbwBQAGEAcwB0AHUAcgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATgAyAE8ARABpAHIAZQBjAHQALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwAzAF8AXwAyAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABUAG8AUABhAHMAdAB1AHIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA1AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADUAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAxAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMQBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADEAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAGkAbABfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADQAXwA3AF8AMQBfADcAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAG8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwBpAGwAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA0AF8ANwBfADEAXwA3AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABvAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AaQBsAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANABfADcAXwAxAF8ANwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAbwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -29448,6 +29502,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
